--- a/human_resources_forms/011_lifestyle_survey--human_resources_forms.xlsx
+++ b/human_resources_forms/011_lifestyle_survey--human_resources_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -980,12 +980,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>employment_status</t>
+          <t>employment_status_2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Employment Status</t>
+          <t>Employment Status 2</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1003,12 +1003,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>job_title</t>
+          <t>job_title_2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Job Title</t>
+          <t>Job Title 2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1026,12 +1026,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>years_in_job</t>
+          <t>years_in_job_2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Years In Job</t>
+          <t>Years In Job 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1049,12 +1049,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>job_satisfaction</t>
+          <t>job_satisfaction_2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Job Satisfaction</t>
+          <t>Job Satisfaction 2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>work_life_balance</t>
+          <t>work_life_balance_2</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Work Life Balance</t>
+          <t>Work Life Balance 2</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1095,12 +1095,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>career_growth</t>
+          <t>career_growth_2</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Career Growth</t>
+          <t>Career Growth 2</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
@@ -1118,12 +1118,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>education</t>
+          <t>education_2</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Education</t>
+          <t>Education 2</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
@@ -1141,12 +1141,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>references</t>
+          <t>references_2</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>References</t>
+          <t>References 2</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
@@ -1170,7 +1170,7 @@
   <dimension ref="A1:C42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="27" customWidth="1" min="1" max="1"/>
+    <col width="29" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="22" customWidth="1" min="3" max="3"/>
   </cols>
@@ -1654,7 +1654,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>employment_status_choices</t>
+          <t>employment_status_2_choices</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1671,7 +1671,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>employment_status_choices</t>
+          <t>employment_status_2_choices</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1688,7 +1688,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>employment_status_choices</t>
+          <t>employment_status_2_choices</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1705,7 +1705,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>employment_status_choices</t>
+          <t>employment_status_2_choices</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1722,7 +1722,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>job_title_choices</t>
+          <t>job_title_2_choices</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1739,7 +1739,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>job_title_choices</t>
+          <t>job_title_2_choices</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1756,7 +1756,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>job_title_choices</t>
+          <t>job_title_2_choices</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1773,7 +1773,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>job_title_choices</t>
+          <t>job_title_2_choices</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1790,7 +1790,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>education_choices</t>
+          <t>education_2_choices</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1807,7 +1807,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>education_choices</t>
+          <t>education_2_choices</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1824,7 +1824,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>education_choices</t>
+          <t>education_2_choices</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1841,7 +1841,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>education_choices</t>
+          <t>education_2_choices</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1858,7 +1858,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>references_choices</t>
+          <t>references_2_choices</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1875,7 +1875,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>references_choices</t>
+          <t>references_2_choices</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
